--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,6 +606,10 @@
   </si>
   <si>
     <t>fr-lm-family-member-history.condition.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3900,13 +3904,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3974,10 +3978,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4003,10 +4007,10 @@
         <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4057,7 +4061,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-family-member-history.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-family-member-history.header.langue</t>
+    <t>fr-lm-family-member-history.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-family-member-history.status</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,13 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Statut de l'entrée provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/R4/valueset-history-status.html</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -452,22 +452,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.language</t>
-  </si>
-  <si>
-    <t>fr-lm-family-member-history.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
-  </si>
-  <si>
-    <t>https://hl7.org/fhir/R4/valueset-history-status.html</t>
   </si>
   <si>
     <t>fr-lm-family-member-history.relatedPerson</t>
@@ -920,7 +904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.55859375" customWidth="true" bestFit="true"/>
@@ -2658,7 +2642,7 @@
         <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2934,10 +2918,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2972,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2983,10 +2967,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2998,13 +2982,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3055,27 +3039,27 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3086,7 +3070,7 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3098,10 +3082,10 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>152</v>
@@ -3155,19 +3139,19 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -3179,14 +3163,14 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3198,15 +3182,17 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3243,43 +3229,43 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3292,24 +3278,26 @@
         <v>73</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>73</v>
       </c>
@@ -3345,19 +3333,19 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3369,51 +3357,47 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
       </c>
@@ -3461,27 +3445,27 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3489,7 +3473,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3507,10 +3491,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3540,10 +3524,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3561,10 +3545,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3578,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3604,7 +3588,7 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>179</v>
@@ -3640,10 +3624,10 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3661,7 +3645,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3678,10 +3662,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3704,13 +3688,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3761,7 +3745,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3778,10 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3804,13 +3788,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3861,7 +3845,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3878,10 +3862,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3904,13 +3888,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3961,7 +3945,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3973,106 +3957,6 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
